--- a/cestas.xlsx
+++ b/cestas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diskol\Documents\CRITICAS CORA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A86586-8718-428E-90A9-85BCC7609F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F59EB6-3F17-467F-AF6F-B3F3E287353C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7D728BE6-9048-4589-B5AB-F22A597A20CD}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="416">
   <si>
     <t>cod</t>
   </si>
@@ -1291,6 +1291,9 @@
   </si>
   <si>
     <t>AGUA MINERAL MINALBA C/GAS GARRAFA VIDRO 300 ML</t>
+  </si>
+  <si>
+    <t>QUINTA DO MORGADO VINHO BRANCO SUAVE GFA VD 750 ML</t>
   </si>
 </sst>
 </file>
@@ -5355,7 +5358,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00965BEA-3F7A-4D6E-8399-48CDDFA08F40}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D407"/>
+  <dimension ref="A1:D408"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -11157,6 +11160,20 @@
         <v>414</v>
       </c>
       <c r="D407" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A408" s="1">
+        <v>24410</v>
+      </c>
+      <c r="B408" t="s">
+        <v>263</v>
+      </c>
+      <c r="C408" t="s">
+        <v>415</v>
+      </c>
+      <c r="D408" t="s">
         <v>308</v>
       </c>
     </row>

--- a/cestas.xlsx
+++ b/cestas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diskol\Documents\CRITICAS CORA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F59EB6-3F17-467F-AF6F-B3F3E287353C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D1D4F0-2DE8-4401-AB89-EFF9AB307A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7D728BE6-9048-4589-B5AB-F22A597A20CD}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="419">
   <si>
     <t>cod</t>
   </si>
@@ -1294,6 +1294,15 @@
   </si>
   <si>
     <t>QUINTA DO MORGADO VINHO BRANCO SUAVE GFA VD 750 ML</t>
+  </si>
+  <si>
+    <t>MALZBIER BRAHMA LATA 350ML SH C/12 NPAL</t>
+  </si>
+  <si>
+    <t>INDAIA AGUA MINERAL C/GAS LATA DE ALUMINIO 269ML CX12</t>
+  </si>
+  <si>
+    <t>ANTARCTICA SUBZERO GFA VD 1L</t>
   </si>
 </sst>
 </file>
@@ -5358,7 +5367,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00965BEA-3F7A-4D6E-8399-48CDDFA08F40}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D408"/>
+  <dimension ref="A1:D411"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -11175,6 +11184,48 @@
       </c>
       <c r="D408" t="s">
         <v>308</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A409">
+        <v>9081</v>
+      </c>
+      <c r="B409" t="s">
+        <v>4</v>
+      </c>
+      <c r="C409" t="s">
+        <v>416</v>
+      </c>
+      <c r="D409" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A410">
+        <v>33233</v>
+      </c>
+      <c r="B410" t="s">
+        <v>263</v>
+      </c>
+      <c r="C410" t="s">
+        <v>417</v>
+      </c>
+      <c r="D410" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A411">
+        <v>10530</v>
+      </c>
+      <c r="B411" t="s">
+        <v>4</v>
+      </c>
+      <c r="C411" t="s">
+        <v>418</v>
+      </c>
+      <c r="D411" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/cestas.xlsx
+++ b/cestas.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diskol\Documents\CRITICAS CORA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F92440BB-009A-4E2A-B1D2-61DE5CC2DE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C19B107-12B4-4A7B-8DCF-0FADD8C30CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BFB5C457-9E5E-4F31-8E2C-ACEC1F112DD6}"/>
   </bookViews>
   <sheets>
     <sheet name="cestas" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cestas!$A$1:$D$431</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="447">
   <si>
     <t>cod</t>
   </si>
@@ -2228,7 +2231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B026D9BF-8D7A-437D-B889-70D659CFF286}">
-  <dimension ref="A1:D432"/>
+  <dimension ref="A1:D431"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -8105,13 +8108,13 @@
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420">
-        <v>29253</v>
+        <v>35526</v>
       </c>
       <c r="B420" t="s">
         <v>269</v>
       </c>
       <c r="C420" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D420" t="s">
         <v>268</v>
@@ -8119,27 +8122,27 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421">
-        <v>35526</v>
+        <v>38406</v>
       </c>
       <c r="B421" t="s">
-        <v>269</v>
+        <v>4</v>
       </c>
       <c r="C421" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D421" t="s">
-        <v>268</v>
+        <v>6</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422">
-        <v>38406</v>
+        <v>4141</v>
       </c>
       <c r="B422" t="s">
         <v>4</v>
       </c>
       <c r="C422" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D422" t="s">
         <v>6</v>
@@ -8147,69 +8150,69 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423">
-        <v>4141</v>
+        <v>7979</v>
       </c>
       <c r="B423" t="s">
-        <v>4</v>
+        <v>212</v>
       </c>
       <c r="C423" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D423" t="s">
-        <v>6</v>
+        <v>212</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424">
-        <v>7979</v>
+        <v>12598</v>
       </c>
       <c r="B424" t="s">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="C424" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D424" t="s">
-        <v>212</v>
+        <v>268</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425">
-        <v>12598</v>
+        <v>20647</v>
       </c>
       <c r="B425" t="s">
-        <v>269</v>
+        <v>4</v>
       </c>
       <c r="C425" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D425" t="s">
-        <v>268</v>
+        <v>6</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>20647</v>
+        <v>31272</v>
       </c>
       <c r="B426" t="s">
-        <v>4</v>
+        <v>212</v>
       </c>
       <c r="C426" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D426" t="s">
-        <v>6</v>
+        <v>214</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>31272</v>
+        <v>32427</v>
       </c>
       <c r="B427" t="s">
         <v>212</v>
       </c>
       <c r="C427" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D427" t="s">
         <v>214</v>
@@ -8217,71 +8220,57 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>32427</v>
+        <v>33235</v>
       </c>
       <c r="B428" t="s">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="C428" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D428" t="s">
-        <v>214</v>
+        <v>268</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>33235</v>
+        <v>34459</v>
       </c>
       <c r="B429" t="s">
         <v>269</v>
       </c>
       <c r="C429" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D429" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A430">
-        <v>34459</v>
+    <row r="430" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A430" s="1">
+        <v>29253</v>
       </c>
       <c r="B430" t="s">
-        <v>269</v>
+        <v>4</v>
       </c>
       <c r="C430" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="D430" t="s">
-        <v>268</v>
+        <v>61</v>
       </c>
     </row>
     <row r="431" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
-        <v>29253</v>
+        <v>33235</v>
       </c>
       <c r="B431" t="s">
-        <v>4</v>
+        <v>269</v>
       </c>
       <c r="C431" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D431" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="432" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A432" s="1">
-        <v>33235</v>
-      </c>
-      <c r="B432" t="s">
-        <v>269</v>
-      </c>
-      <c r="C432" t="s">
-        <v>445</v>
-      </c>
-      <c r="D432" t="s">
         <v>268</v>
       </c>
     </row>
